--- a/Employee_Reports_wi52/Abdunaser Ahmed Aragaw Q0042.xlsx
+++ b/Employee_Reports_wi52/Abdunaser Ahmed Aragaw Q0042.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -652,11 +652,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
